--- a/data/trans_orig/IP07C11-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07C11-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse feliz en casa en 2007 (tasa de respuesta: 89,89%)</t>
+          <t>Menores según la frecuencia de sentirse feliz en casa en 2007 (tasa de respuesta: 89,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28919</t>
+          <t>29488</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41149</t>
+          <t>41050</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>51,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36935</t>
+          <t>36827</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49662</t>
+          <t>49362</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>70154</t>
+          <t>69857</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>87547</t>
+          <t>87769</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>69,95%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14449</t>
+          <t>14897</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26027</t>
+          <t>26065</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17368</t>
+          <t>17601</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29706</t>
+          <t>29200</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35474</t>
+          <t>35322</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52868</t>
+          <t>52296</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>41,68%</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3692</t>
+          <t>3637</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4961</t>
+          <t>4204</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>610</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>5856</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3620</t>
+          <t>3184</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3509</t>
+          <t>3869</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52240</t>
+          <t>52434</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>67740</t>
+          <t>68172</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>48668</t>
+          <t>48545</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63743</t>
+          <t>63408</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>105734</t>
+          <t>106296</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>126682</t>
+          <t>127137</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,46%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26183</t>
+          <t>25817</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41452</t>
+          <t>40899</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24953</t>
+          <t>25535</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39340</t>
+          <t>39592</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>55013</t>
+          <t>55224</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>75302</t>
+          <t>75318</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2595</t>
+          <t>2585</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10101</t>
+          <t>9801</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1356</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7708</t>
+          <t>8659</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>5209</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>14616</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3281</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2957</t>
+          <t>3271</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30778</t>
+          <t>30868</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41644</t>
+          <t>41732</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36516</t>
+          <t>36715</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47479</t>
+          <t>47761</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>70328</t>
+          <t>70838</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>86192</t>
+          <t>86469</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>73,89%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13021</t>
+          <t>13231</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23816</t>
+          <t>23868</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12042</t>
+          <t>11775</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22698</t>
+          <t>22586</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27968</t>
+          <t>27772</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43740</t>
+          <t>42632</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>36,43%</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3464</t>
+          <t>3628</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>707</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5837</t>
+          <t>5749</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1177</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7513</t>
+          <t>7210</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39006</t>
+          <t>38876</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53707</t>
+          <t>53509</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>68,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>52312</t>
+          <t>52160</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>66137</t>
+          <t>66152</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>59,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>94931</t>
+          <t>95964</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>115581</t>
+          <t>116428</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,95%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>19561</t>
+          <t>18856</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>33914</t>
+          <t>32952</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>17895</t>
+          <t>17519</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>30736</t>
+          <t>31445</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>40292</t>
+          <t>40260</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>60177</t>
+          <t>60448</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,32%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2132</t>
+          <t>1602</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9602</t>
+          <t>9596</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2167</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10125</t>
+          <t>9032</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4695</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>14762</t>
+          <t>14679</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4744</t>
+          <t>4983</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4332</t>
+          <t>5016</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>163826</t>
+          <t>163944</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>190766</t>
+          <t>191355</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>187027</t>
+          <t>188840</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>213376</t>
+          <t>214901</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>362426</t>
+          <t>361287</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>399259</t>
+          <t>398761</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>66,44%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>85997</t>
+          <t>84056</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>111720</t>
+          <t>112731</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>83593</t>
+          <t>83714</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>109153</t>
+          <t>107395</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>174038</t>
+          <t>174295</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>210663</t>
+          <t>211281</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,2%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6879</t>
+          <t>7267</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>18345</t>
+          <t>18828</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7410</t>
+          <t>7637</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>18361</t>
+          <t>19343</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>17198</t>
+          <t>16652</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>32575</t>
+          <t>32621</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>675</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6270</t>
+          <t>6709</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>731</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6698</t>
+          <t>6758</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse feliz en casa en 2012 (tasa de respuesta: 95,72%)</t>
+          <t>Menores según la frecuencia de sentirse feliz en casa en 2012 (tasa de respuesta: 95,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38192</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50541</t>
+          <t>50141</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>45307</t>
+          <t>45030</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58241</t>
+          <t>58000</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>88100</t>
+          <t>88667</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>106248</t>
+          <t>104924</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>65,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>77,48%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11776</t>
+          <t>12071</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23465</t>
+          <t>23371</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13302</t>
+          <t>13188</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26232</t>
+          <t>25922</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27100</t>
+          <t>28325</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44947</t>
+          <t>45291</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,44%</t>
         </is>
       </c>
     </row>
@@ -4605,7 +4605,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4349</t>
+          <t>5041</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3210</t>
+          <t>3448</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>631</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6207</t>
+          <t>5393</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>72409</t>
+          <t>72169</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50833</t>
+          <t>51133</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66706</t>
+          <t>66276</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>114086</t>
+          <t>114411</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>135123</t>
+          <t>134701</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>69,79%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23045</t>
+          <t>23325</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37527</t>
+          <t>37861</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27480</t>
+          <t>27069</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43049</t>
+          <t>42050</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>54093</t>
+          <t>53621</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>74680</t>
+          <t>74375</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,54%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5471</t>
+          <t>5387</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>621</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4998</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7920</t>
+          <t>7857</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2548</t>
+          <t>3701</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>4143</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35752</t>
+          <t>35193</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48151</t>
+          <t>48325</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,82 +5753,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>74,16%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>48320</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>41889</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>54078</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>69,95%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>60,64%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>78,28%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>90592</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>82229</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>99193</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>67,48%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>61,25%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
           <t>73,89%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>48320</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>41784</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>53686</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>69,95%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>60,48%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>77,71%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>90592</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>81166</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>99210</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>67,48%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>60,46%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>73,9%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14941</t>
+          <t>14798</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27322</t>
+          <t>27561</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13073</t>
+          <t>12439</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24734</t>
+          <t>24368</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>30510</t>
+          <t>30228</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48097</t>
+          <t>46871</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>34,91%</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5920</t>
+          <t>5437</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>574</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>5862</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1797</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8977</t>
+          <t>9664</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -6117,7 +6117,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3564</t>
+          <t>2924</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39216</t>
+          <t>38938</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>55228</t>
+          <t>55287</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>47601</t>
+          <t>46976</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>63128</t>
+          <t>62926</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,26%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>91187</t>
+          <t>91440</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>113367</t>
+          <t>114204</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>65,04%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>28762</t>
+          <t>27934</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>44100</t>
+          <t>44066</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>20364</t>
+          <t>21209</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>35524</t>
+          <t>36322</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>52598</t>
+          <t>52340</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>74462</t>
+          <t>75180</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,82%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>723</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7468</t>
+          <t>7795</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3013</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11681</t>
+          <t>11372</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5079</t>
+          <t>5030</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>15651</t>
+          <t>16506</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>185963</t>
+          <t>184454</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>214592</t>
+          <t>212799</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>200874</t>
+          <t>201709</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>229545</t>
+          <t>228517</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>395745</t>
+          <t>396382</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>433429</t>
+          <t>434294</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>68,04%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>89724</t>
+          <t>90141</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>116282</t>
+          <t>117949</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>85552</t>
+          <t>86717</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>112466</t>
+          <t>112985</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>184366</t>
+          <t>181294</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>222057</t>
+          <t>220176</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,5%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>14419</t>
+          <t>14264</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6425</t>
+          <t>6455</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>17163</t>
+          <t>17524</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>13237</t>
+          <t>13077</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>27804</t>
+          <t>28002</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -7446,7 +7446,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>3315</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2923</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7516,7 +7516,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>4221</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse feliz en casa en 2016 (tasa de respuesta: 95,67%)</t>
+          <t>Menores según la frecuencia de sentirse feliz en casa en 2016 (tasa de respuesta: 95,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43237</t>
+          <t>44369</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>56237</t>
+          <t>56569</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44949</t>
+          <t>44197</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57328</t>
+          <t>57349</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>94132</t>
+          <t>93783</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>111327</t>
+          <t>111480</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,6%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9312</t>
+          <t>8989</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21290</t>
+          <t>20396</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9559</t>
+          <t>9217</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21095</t>
+          <t>21111</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21098</t>
+          <t>21382</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36821</t>
+          <t>37081</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,48%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8615</t>
+          <t>8055</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2161</t>
+          <t>2146</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9135</t>
+          <t>9579</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4599</t>
+          <t>4779</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14797</t>
+          <t>15331</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52068</t>
+          <t>53015</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68009</t>
+          <t>68308</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>58103</t>
+          <t>56787</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>74030</t>
+          <t>73691</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>114369</t>
+          <t>114232</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>136832</t>
+          <t>137287</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,56%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24169</t>
+          <t>24469</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40202</t>
+          <t>38981</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26667</t>
+          <t>26506</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42411</t>
+          <t>42957</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>55211</t>
+          <t>55644</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>76548</t>
+          <t>76602</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,14%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5548</t>
+          <t>5095</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15255</t>
+          <t>15071</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7927</t>
+          <t>7851</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8063</t>
+          <t>8300</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19453</t>
+          <t>19908</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -9042,7 +9042,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2830</t>
+          <t>2378</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2835</t>
+          <t>2839</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9127,7 +9127,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3092</t>
+          <t>3118</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3749</t>
+          <t>3089</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39437</t>
+          <t>39777</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>52310</t>
+          <t>52194</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>43300</t>
+          <t>44160</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>57119</t>
+          <t>57336</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>88129</t>
+          <t>87399</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>106947</t>
+          <t>106145</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>73,44%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15429</t>
+          <t>15882</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28277</t>
+          <t>27705</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15863</t>
+          <t>15984</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29328</t>
+          <t>29078</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34783</t>
+          <t>35293</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>53352</t>
+          <t>53606</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>37,09%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>615</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5358</t>
+          <t>5503</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3804</t>
+          <t>3806</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>710</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6983</t>
+          <t>6623</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -9759,7 +9759,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3855</t>
+          <t>3886</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3736</t>
+          <t>3839</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>48585</t>
+          <t>48540</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>66886</t>
+          <t>65866</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>48092</t>
+          <t>49187</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>65772</t>
+          <t>65969</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>103659</t>
+          <t>102792</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>127862</t>
+          <t>126409</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>62,14%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>32541</t>
+          <t>31591</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>50359</t>
+          <t>49179</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>29288</t>
+          <t>29623</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>46705</t>
+          <t>46823</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>65975</t>
+          <t>67086</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>89607</t>
+          <t>90187</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,34%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1603</t>
+          <t>1582</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9622</t>
+          <t>9312</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9665</t>
+          <t>9136</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5106</t>
+          <t>5208</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>15813</t>
+          <t>14945</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4449</t>
+          <t>4163</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10421,7 +10421,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10476,7 +10476,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3875</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>198021</t>
+          <t>199921</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>229982</t>
+          <t>231024</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>209830</t>
+          <t>209938</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>239751</t>
+          <t>241555</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>419028</t>
+          <t>417892</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>461240</t>
+          <t>460562</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,34%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>92754</t>
+          <t>93947</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>122660</t>
+          <t>122777</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>94889</t>
+          <t>94567</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>124017</t>
+          <t>124415</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>196382</t>
+          <t>197385</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>237216</t>
+          <t>238737</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,39%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>13668</t>
+          <t>13411</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>27390</t>
+          <t>27143</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8735</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>21363</t>
+          <t>21082</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>25373</t>
+          <t>25699</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>43980</t>
+          <t>43448</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -11088,7 +11088,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4455</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11103,7 +11103,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11123,7 +11123,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>563</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5987</t>
+          <t>5996</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11201,7 +11201,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2958</t>
+          <t>3663</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11271,7 +11271,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2485</t>
+          <t>3097</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11286,7 +11286,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
